--- a/wwwroot/55/ExtrasCalculation.xlsx
+++ b/wwwroot/55/ExtrasCalculation.xlsx
@@ -1610,7 +1610,7 @@
         <v>69</v>
       </c>
       <c r="F11" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G11" s="0" t="s">
         <v>35</v>
@@ -4260,7 +4260,7 @@
         <v>69</v>
       </c>
       <c r="F61" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G61" s="0" t="s">
         <v>35</v>
@@ -6327,7 +6327,7 @@
         <v>69</v>
       </c>
       <c r="F100" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G100" s="0" t="s">
         <v>35</v>
@@ -8447,7 +8447,7 @@
         <v>69</v>
       </c>
       <c r="F140" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G140" s="0" t="s">
         <v>35</v>
@@ -9719,7 +9719,7 @@
         <v>69</v>
       </c>
       <c r="F164" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G164" s="0" t="s">
         <v>35</v>
@@ -11574,7 +11574,7 @@
         <v>69</v>
       </c>
       <c r="F199" s="0" t="s">
-        <v>22</v>
+        <v>41</v>
       </c>
       <c r="G199" s="0" t="s">
         <v>35</v>
